--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="15.33203125" customWidth="1" style="8" min="4" max="5"/>
@@ -885,7 +885,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" s="8">
       <c r="A6" s="26" t="n"/>
       <c r="B6" s="26" t="n">
         <v>20004</v>
@@ -938,6 +938,59 @@
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="26" t="n"/>
     </row>
+    <row r="7" s="8">
+      <c r="A7" s="26" t="n"/>
+      <c r="B7" s="26" t="n">
+        <v>20010</v>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>Flamethrower</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>持续喷火：角色命中走正式 GameplayEffect，地表反应走 TaskApplyWorldElement</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="n"/>
+      <c r="F7" s="26" t="n"/>
+      <c r="G7" s="26" t="n"/>
+      <c r="H7" s="26" t="n"/>
+      <c r="I7" s="26" t="n"/>
+      <c r="J7" s="26" t="n"/>
+      <c r="K7" s="26" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="n"/>
+      <c r="M7" s="26" t="inlineStr">
+        <is>
+          <t>0;0;3003</t>
+        </is>
+      </c>
+      <c r="N7" s="26" t="inlineStr">
+        <is>
+          <t>ALTimeline</t>
+        </is>
+      </c>
+      <c r="O7" s="26" t="n">
+        <v>20010</v>
+      </c>
+      <c r="P7" s="26" t="n"/>
+      <c r="Q7" s="26" t="n"/>
+      <c r="R7" s="26" t="n"/>
+      <c r="S7" s="26" t="n"/>
+      <c r="T7" s="26" t="n"/>
+      <c r="U7" s="26" t="n"/>
+      <c r="V7" s="26" t="n"/>
+      <c r="W7" s="26" t="n"/>
+      <c r="X7" s="26" t="n"/>
+      <c r="Y7" s="26" t="n"/>
+      <c r="Z7" s="26" t="n"/>
+      <c r="AA7" s="26" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="N1:AA1"/>
